--- a/output/pdf_financials_xlsx/CMIL.xlsx
+++ b/output/pdf_financials_xlsx/CMIL.xlsx
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.512765</v>
+        <v>-1.512765</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.20957</v>
+        <v>-0.20957</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.528434</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.512765</v>
+        <v>-1.512765</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.20957</v>
+        <v>-0.20957</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.528434</v>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.512765</v>
+        <v>-1.512765</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.20957</v>
+        <v>-0.20957</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.528434</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>7.961921</v>
+        <v>-7.961921</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>6.985667</v>
+        <v>-6.985667</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>10.56868</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.512765</v>
+        <v>-1.512765</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.20957</v>
+        <v>-0.20957</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.528434</v>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.512765</v>
+        <v>-1.512765</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.20957</v>
+        <v>-0.20957</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.528434</v>
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -19983,10 +19983,10 @@
         </is>
       </c>
       <c r="E192" s="5" t="n">
-        <v>1.512765</v>
+        <v>-1.512765</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>0.20957</v>
+        <v>-0.20957</v>
       </c>
       <c r="G192" s="5" t="n">
         <v>-0.528434</v>

--- a/output/pdf_financials_xlsx/CMIL.xlsx
+++ b/output/pdf_financials_xlsx/CMIL.xlsx
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.589351</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.560144</v>
@@ -2096,25 +2096,25 @@
         <v>0.257839</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.637549</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.07377300000000001</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.043219</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.103663</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.057973</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.061409</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.033629</v>
       </c>
     </row>
     <row r="35">
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.589351</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.560144</v>
@@ -2176,25 +2176,25 @@
         <v>0.257839</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.637549</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.07377300000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.043219</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.103663</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.057973</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.061409</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.033629</v>
       </c>
     </row>
     <row r="37">
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.601274</v>
+        <v>0.011923</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -2656,25 +2656,25 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.638186</v>
+        <v>0.000637</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.08728900000000001</v>
+        <v>0.013516</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.057982</v>
+        <v>0.014763</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.258553</v>
+        <v>0.15489</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.095404</v>
+        <v>0.037431</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.149738</v>
+        <v>0.088329</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.048127</v>
+        <v>0.014498</v>
       </c>
     </row>
     <row r="49">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
@@ -13833,7 +13833,11 @@
           <t>Reclamation deposits (Note 12)</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E104" s="5" t="n">
         <v>0.011923</v>
       </c>
@@ -17414,7 +17418,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
